--- a/results/02_taxa_assemblage/tables/anova_taxa.xlsx
+++ b/results/02_taxa_assemblage/tables/anova_taxa.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,11 +474,6 @@
           <t>Cluster C2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster C3</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -486,23 +481,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dreissena</t>
+          <t>Hydropsychidae</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>157.9</v>
+        <v>76.05</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>26.75</v>
+        <v>13.27</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>126.93</v>
+        <v>252.2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +506,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.52 ± 0.14</t>
+          <t>0.16 ± 0.09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.16 ± 0.26</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>5.20 ± 0.27</t>
+          <t>4.73 ± 0.21</t>
         </is>
       </c>
     </row>
@@ -531,23 +521,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hydropsychidae</t>
+          <t>Other Trichoptera</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>76.27</v>
+        <v>31.87</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>13.04</v>
+        <v>33.13</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>125.72</v>
+        <v>42.33</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -556,17 +546,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.20 ± 0.10</t>
+          <t>0.32 ± 0.12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.73 ± 0.21</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
+          <t>3.27 ± 0.87</t>
         </is>
       </c>
     </row>
@@ -576,42 +561,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other Trichoptera</t>
+          <t>Dreissena</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32.73</v>
+        <v>29.8</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>32.27</v>
+        <v>154.84</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>21.81</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0000***</t>
+          <t>0.0056**</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.38 ± 0.14</t>
+          <t>1.30 ± 0.30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3.27 ± 0.87</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
+          <t>4.16 ± 0.26</t>
         </is>
       </c>
     </row>
@@ -621,42 +601,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chironomidae</t>
+          <t>Hydrozoa</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40.61</v>
+        <v>7.73</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>79.28</v>
+        <v>41.79</v>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>11.01</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0001***</t>
+          <t>0.0066**</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.93 ± 0.22</t>
+          <t>0.35 ± 0.12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.61 ± 0.19</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2.39 ± 0.69</t>
+          <t>1.81 ± 1.14</t>
         </is>
       </c>
     </row>
@@ -670,38 +645,33 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.18</v>
+        <v>7.59</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>42.65</v>
+        <v>44.24</v>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>4.63</v>
+        <v>7.55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0151*</t>
+          <t>0.0087**</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.52 ± 0.18</t>
+          <t>0.43 ± 0.16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>1.88 ± 0.42</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -711,42 +681,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hydrozoa</t>
+          <t>Oligochaeta</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.91</v>
+        <v>10.12</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>41.61</v>
+        <v>63.56</v>
       </c>
       <c r="F7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>4.09</v>
+        <v>7.01</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0237*</t>
+          <t>0.0112*</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.38 ± 0.14</t>
+          <t>4.99 ± 0.19</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.81 ± 1.14</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.21 ± 0.21</t>
+          <t>3.32 ± 0.54</t>
         </is>
       </c>
     </row>
@@ -756,42 +721,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oligochaeta</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10.26</v>
+        <v>14.58</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>63.43</v>
+        <v>112.73</v>
       </c>
       <c r="F8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>3.48</v>
+        <v>5.69</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0398*</t>
+          <t>0.0214*</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.96 ± 0.22</t>
+          <t>2.37 ± 0.25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.32 ± 0.54</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>5.11 ± 0.23</t>
+          <t>0.38 ± 0.38</t>
         </is>
       </c>
     </row>
@@ -801,42 +761,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nematoda</t>
+          <t>Hirudinea</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.63</v>
+        <v>0.84</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>109.68</v>
+        <v>14.69</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>3.45</v>
+        <v>2.51</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0406*</t>
+          <t>0.1202</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.25 ± 0.28</t>
+          <t>0.15 ± 0.08</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.38 ± 0.38</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2.98 ± 0.58</t>
+          <t>0.63 ± 0.63</t>
         </is>
       </c>
     </row>
@@ -846,42 +801,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Turbellaria</t>
+          <t>Gastropoda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.71</v>
+        <v>3.85</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>21.84</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>2.67</v>
+        <v>2.21</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0809.</t>
+          <t>0.1443</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.33 ± 0.11</t>
+          <t>0.78 ± 0.20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.92 ± 0.44</t>
+          <t>1.81 ± 0.71</t>
         </is>
       </c>
     </row>
@@ -891,42 +841,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hirudinea</t>
+          <t>Turbellaria</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.87</v>
+        <v>0.67</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>14.66</v>
+        <v>23.89</v>
       </c>
       <c r="F11" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.2899</t>
+          <t>0.2744</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.16 ± 0.09</t>
+          <t>0.43 ± 0.12</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.63 ± 0.63</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.09 ± 0.09</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -936,42 +881,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gastropoda</t>
+          <t>Chironomidae</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3.94</v>
+        <v>2.91</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>76.63</v>
+        <v>116.98</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.3008</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.80 ± 0.23</t>
+          <t>4.50 ± 0.26</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.81 ± 0.71</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0.68 ± 0.44</t>
+          <t>3.61 ± 0.19</t>
         </is>
       </c>
     </row>
@@ -981,42 +921,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Acari</t>
+          <t>Hexagenia</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.24</v>
+        <v>0.93</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>31.7</v>
+        <v>43.13</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.4384</t>
+          <t>0.3357</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.65 ± 0.15</t>
+          <t>0.50 ± 0.16</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.73 ± 0.46</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0.20 ± 0.14</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
     </row>
@@ -1026,42 +961,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ceratopogonidae</t>
+          <t>Sphaeriidae</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.27</v>
+        <v>0.49</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>7.37</v>
+        <v>62.57</v>
       </c>
       <c r="F14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>0.79</v>
+        <v>0.35</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.4606</t>
+          <t>0.5587</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.07 ± 0.06</t>
+          <t>0.87 ± 0.19</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.27 ± 0.27</t>
+          <t>0.51 ± 0.35</t>
         </is>
       </c>
     </row>
@@ -1071,42 +1001,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hexagenia</t>
+          <t>Ceratopogonidae</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.96</v>
+        <v>0.04</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>43.1</v>
+        <v>7.6</v>
       </c>
       <c r="F15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>0.48</v>
+        <v>0.24</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.6222</t>
+          <t>0.6259</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.49 ± 0.18</t>
+          <t>0.11 ± 0.07</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0.57 ± 0.40</t>
         </is>
       </c>
     </row>
@@ -1116,42 +1041,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Caenis</t>
+          <t>Acari</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.77</v>
+        <v>0.09</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>40.3</v>
+        <v>32.85</v>
       </c>
       <c r="F16" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G16" t="n">
-        <v>0.41</v>
+        <v>0.13</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.6664</t>
+          <t>0.7235</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.51 ± 0.18</t>
+          <t>0.57 ± 0.13</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.39 ± 0.39</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0.15 ± 0.15</t>
+          <t>0.73 ± 0.46</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1081,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sphaeriidae</t>
+          <t>Caenis</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5</v>
+        <v>0.01</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>62.56</v>
+        <v>41.06</v>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G17" t="n">
-        <v>0.17</v>
+        <v>0.02</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.8421</t>
+          <t>0.9012</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.87 ± 0.21</t>
+          <t>0.45 ± 0.15</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.51 ± 0.35</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0.90 ± 0.42</t>
+          <t>0.39 ± 0.39</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1128,6 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1231,13 +1145,10 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J19" t="n">
         <v>4</v>
-      </c>
-      <c r="K19" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -1253,7 +1164,6 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1272,7 +1182,6 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/02_taxa_assemblage/tables/anova_taxa.xlsx
+++ b/results/02_taxa_assemblage/tables/anova_taxa.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>Cluster C2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster C3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -481,23 +486,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hydropsychidae</t>
+          <t>Dreissena</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>76.05</v>
+        <v>284.88</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>13.27</v>
+        <v>60.37</v>
       </c>
       <c r="F2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>252.2</v>
+        <v>101.46</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -506,12 +511,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.16 ± 0.09</t>
+          <t>2.56 ± 0.87</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.73 ± 0.21</t>
+          <t>6.23 ± 0.10</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.19 ± 0.08</t>
         </is>
       </c>
     </row>
@@ -521,23 +531,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other Trichoptera</t>
+          <t>Chironomidae</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>31.87</v>
+        <v>158.33</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>33.13</v>
+        <v>70.62</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>42.33</v>
+        <v>48.21</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -546,12 +556,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.32 ± 0.12</t>
+          <t>2.06 ± 0.65</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.27 ± 0.87</t>
+          <t>1.08 ± 0.33</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>5.20 ± 0.21</t>
         </is>
       </c>
     </row>
@@ -561,37 +576,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dreissena</t>
+          <t>Oligochaeta</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29.8</v>
+        <v>94.22</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>154.84</v>
+        <v>99.01000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
-        <v>8.470000000000001</v>
+        <v>20.46</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0056**</t>
+          <t>0.0000***</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.30 ± 0.30</t>
+          <t>5.39 ± 0.30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.16 ± 0.26</t>
+          <t>1.35 ± 0.49</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>4.25 ± 0.32</t>
         </is>
       </c>
     </row>
@@ -601,37 +621,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hydrozoa</t>
+          <t>Amphipoda</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.73</v>
+        <v>46.57</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>41.79</v>
+        <v>107.19</v>
       </c>
       <c r="F5" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G5" t="n">
-        <v>8.140000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0066**</t>
+          <t>0.0004***</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.35 ± 0.12</t>
+          <t>1.02 ± 0.68</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.81 ± 1.14</t>
+          <t>3.19 ± 0.60</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.78 ± 0.23</t>
         </is>
       </c>
     </row>
@@ -641,37 +666,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amphipoda</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7.59</v>
+        <v>41.37</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>44.24</v>
+        <v>134.18</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>7.55</v>
+        <v>6.63</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0087**</t>
+          <t>0.0031**</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.43 ± 0.16</t>
+          <t>2.75 ± 0.59</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.88 ± 0.42</t>
+          <t>0.38 ± 0.17</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2.54 ± 0.40</t>
         </is>
       </c>
     </row>
@@ -681,37 +711,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Oligochaeta</t>
+          <t>Caenis</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10.12</v>
+        <v>11.83</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>63.56</v>
+        <v>69.97</v>
       </c>
       <c r="F7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
-        <v>7.01</v>
+        <v>3.64</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0112*</t>
+          <t>0.0347*</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.99 ± 0.19</t>
+          <t>0.09 ± 0.06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.32 ± 0.54</t>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1.06 ± 0.33</t>
         </is>
       </c>
     </row>
@@ -721,37 +756,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nematoda</t>
+          <t>Acari</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14.58</v>
+        <v>3.36</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>112.73</v>
+        <v>24.98</v>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G8" t="n">
-        <v>5.69</v>
+        <v>2.89</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0214*</t>
+          <t>0.0663.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.37 ± 0.25</t>
+          <t>0.37 ± 0.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.38 ± 0.38</t>
+          <t>0.05 ± 0.05</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.70 ± 0.19</t>
         </is>
       </c>
     </row>
@@ -761,37 +801,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hirudinea</t>
+          <t>Gastropoda</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.84</v>
+        <v>5.04</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>14.69</v>
+        <v>45.93</v>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
-        <v>2.51</v>
+        <v>2.36</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.1202</t>
+          <t>0.1066</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.15 ± 0.08</t>
+          <t>1.00 ± 0.66</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.63 ± 0.63</t>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.37 ± 0.15</t>
         </is>
       </c>
     </row>
@@ -801,37 +846,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gastropoda</t>
+          <t>Hydrozoa</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.85</v>
+        <v>1.42</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>76.70999999999999</v>
+        <v>13.66</v>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.1443</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.78 ± 0.20</t>
+          <t>0.16 ± 0.16</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.81 ± 0.71</t>
+          <t>0.53 ± 0.29</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.11 ± 0.06</t>
         </is>
       </c>
     </row>
@@ -845,33 +895,38 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.67</v>
+        <v>1.58</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>23.89</v>
+        <v>17.94</v>
       </c>
       <c r="F11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G11" t="n">
-        <v>1.23</v>
+        <v>1.89</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.2744</t>
+          <t>0.1632</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.43 ± 0.12</t>
+          <t>0.57 ± 0.37</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.24 ± 0.24</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.08 ± 0.05</t>
         </is>
       </c>
     </row>
@@ -881,37 +936,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chironomidae</t>
+          <t>Hydropsychidae</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.91</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>116.98</v>
+        <v>12.97</v>
       </c>
       <c r="F12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.3008</t>
+          <t>0.2721</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.50 ± 0.26</t>
+          <t>0.11 ± 0.11</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.61 ± 0.19</t>
+          <t>0.49 ± 0.21</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.22 ± 0.11</t>
         </is>
       </c>
     </row>
@@ -921,37 +981,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hexagenia</t>
+          <t>Hirudinea</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>43.13</v>
+        <v>19.5</v>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>0.95</v>
+        <v>1.18</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.3357</t>
+          <t>0.3172</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.50 ± 0.16</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.31 ± 0.17</t>
         </is>
       </c>
     </row>
@@ -965,33 +1030,38 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.49</v>
+        <v>2.04</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>62.57</v>
+        <v>38.6</v>
       </c>
       <c r="F14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G14" t="n">
-        <v>0.35</v>
+        <v>1.14</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.5587</t>
+          <t>0.3299</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.87 ± 0.19</t>
+          <t>0.40 ± 0.30</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.51 ± 0.35</t>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.51 ± 0.22</t>
         </is>
       </c>
     </row>
@@ -1001,37 +1071,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ceratopogonidae</t>
+          <t>Hexagenia</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.04</v>
+        <v>2.09</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>7.6</v>
+        <v>43.03</v>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G15" t="n">
-        <v>0.24</v>
+        <v>1.04</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.6259</t>
+          <t>0.3607</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.11 ± 0.07</t>
+          <t>0.14 ± 0.14</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.18 ± 0.18</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0.59 ± 0.24</t>
         </is>
       </c>
     </row>
@@ -1041,37 +1116,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Acari</t>
+          <t>Ceratopogonidae</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>32.85</v>
+        <v>4.37</v>
       </c>
       <c r="F16" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
-        <v>0.13</v>
+        <v>0.58</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.7235</t>
+          <t>0.5665</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.57 ± 0.13</t>
+          <t>0.04 ± 0.04</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.73 ± 0.46</t>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0.12 ± 0.08</t>
         </is>
       </c>
     </row>
@@ -1081,37 +1161,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Caenis</t>
+          <t>Other Trichoptera</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>41.06</v>
+        <v>3.89</v>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
-        <v>0.02</v>
+        <v>0.37</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.9012</t>
+          <t>0.6903</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.45 ± 0.15</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.39 ± 0.39</t>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0.08 ± 0.08</t>
         </is>
       </c>
     </row>
@@ -1128,6 +1213,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1145,10 +1231,13 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>11</v>
+      </c>
+      <c r="K19" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1164,6 +1253,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1182,6 +1272,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
